--- a/data/species_key.xlsx
+++ b/data/species_key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Library/CloudStorage/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C306D098-41E6-A14B-B7BB-A9F135ED6978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44400" yWindow="3860" windowWidth="28040" windowHeight="17440" xr2:uid="{59FED1E9-671D-A14E-97CD-E39A7C3D0157}"/>
+    <workbookView xWindow="36740" yWindow="3940" windowWidth="28040" windowHeight="17440" xr2:uid="{59FED1E9-671D-A14E-97CD-E39A7C3D0157}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
